--- a/artfynd/A 2044-2026 artfynd.xlsx
+++ b/artfynd/A 2044-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1015,6 +1015,1752 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130872700</v>
+      </c>
+      <c r="B5" t="n">
+        <v>78978</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Flytjärnsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>571145</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6736812</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130872697</v>
+      </c>
+      <c r="B6" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Flytjärnsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>570626</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6736614</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130872713</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Flytjärnsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>570831</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6736787</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130872699</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78978</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Flytjärnsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>571131</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6736687</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130872707</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Flytjärnsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>570828</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6736602</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130872710</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Flytjärnsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>570585</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6736756</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130872720</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Flytjärnsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>571020</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6736588</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>130872698</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78978</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Flytjärnsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>570821</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6736787</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130872695</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78979</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Flytjärnsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>570816</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6736802</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>130872717</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Flytjärnsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>571254</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6736578</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130872715</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Flytjärnsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>571193</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6736684</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>130872718</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Flytjärnsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>571142</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6736599</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>130872714</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Flytjärnsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>570912</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6736673</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>130872709</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Flytjärnsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>570714</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6736567</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>130872711</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Flytjärnsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>570602</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6736798</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>130872696</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78979</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Flytjärnsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>571194</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6736752</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>130872725</v>
+      </c>
+      <c r="B21" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Flytjärnsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>570869</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6736590</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>130872716</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Flytjärnsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>570988</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6736647</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2044-2026 artfynd.xlsx
+++ b/artfynd/A 2044-2026 artfynd.xlsx
@@ -1114,32 +1114,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130872697</v>
+        <v>130872713</v>
       </c>
       <c r="B6" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1149,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570626</v>
+        <v>570831</v>
       </c>
       <c r="R6" t="n">
-        <v>6736614</v>
+        <v>6736787</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1211,32 +1211,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130872713</v>
+        <v>130872697</v>
       </c>
       <c r="B7" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570831</v>
+        <v>570626</v>
       </c>
       <c r="R7" t="n">
-        <v>6736787</v>
+        <v>6736614</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1793,10 +1793,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130872695</v>
+        <v>130872717</v>
       </c>
       <c r="B13" t="n">
-        <v>78979</v>
+        <v>79221</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1804,21 +1804,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1828,10 +1828,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>570816</v>
+        <v>571254</v>
       </c>
       <c r="R13" t="n">
-        <v>6736802</v>
+        <v>6736578</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1890,10 +1890,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130872717</v>
+        <v>130872695</v>
       </c>
       <c r="B14" t="n">
-        <v>79221</v>
+        <v>78979</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1901,21 +1901,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1925,10 +1925,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>571254</v>
+        <v>570816</v>
       </c>
       <c r="R14" t="n">
-        <v>6736578</v>
+        <v>6736802</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2569,32 +2569,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130872725</v>
+        <v>130872716</v>
       </c>
       <c r="B21" t="n">
-        <v>5177</v>
+        <v>79221</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>570869</v>
+        <v>570988</v>
       </c>
       <c r="R21" t="n">
-        <v>6736590</v>
+        <v>6736647</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2666,32 +2666,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130872716</v>
+        <v>130872725</v>
       </c>
       <c r="B22" t="n">
-        <v>79221</v>
+        <v>5177</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>570988</v>
+        <v>570869</v>
       </c>
       <c r="R22" t="n">
-        <v>6736647</v>
+        <v>6736590</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>

--- a/artfynd/A 2044-2026 artfynd.xlsx
+++ b/artfynd/A 2044-2026 artfynd.xlsx
@@ -2763,10 +2763,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130983610</v>
+        <v>130979096</v>
       </c>
       <c r="B23" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2794,17 +2794,17 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Flytjärnsmyren, Dlr</t>
+          <t>Flytjärnsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>571415</v>
+        <v>571617</v>
       </c>
       <c r="R23" t="n">
-        <v>6736599</v>
+        <v>6736718</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2831,19 +2831,9 @@
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-01-31</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>10:37</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2858,22 +2848,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130979096</v>
+        <v>130983610</v>
       </c>
       <c r="B24" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2901,17 +2891,17 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Flytjärnsmyran, Dlr</t>
+          <t>Flytjärnsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>571617</v>
+        <v>571415</v>
       </c>
       <c r="R24" t="n">
-        <v>6736718</v>
+        <v>6736599</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2938,9 +2928,19 @@
           <t>2026-01-31</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2955,22 +2955,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130983063</v>
+        <v>130979083</v>
       </c>
       <c r="B25" t="n">
-        <v>8451</v>
+        <v>57073</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2978,46 +2978,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Flytjärnsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>570956</v>
+        <v>570745</v>
       </c>
       <c r="R25" t="n">
-        <v>6736657</v>
+        <v>6736794</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3044,19 +3035,14 @@
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>09:32</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>09:32</t>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färsk spillning</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3065,29 +3051,28 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130979083</v>
+        <v>130983063</v>
       </c>
       <c r="B26" t="n">
-        <v>57073</v>
+        <v>8451</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3095,37 +3080,46 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Flytjärnsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>570745</v>
+        <v>570956</v>
       </c>
       <c r="R26" t="n">
-        <v>6736794</v>
+        <v>6736657</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3152,14 +3146,19 @@
           <t>2026-01-31</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Färsk spillning</t>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3168,18 +3167,19 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3189,7 +3189,7 @@
         <v>130983609</v>
       </c>
       <c r="B27" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3293,10 +3293,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130979098</v>
+        <v>130979095</v>
       </c>
       <c r="B28" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571475</v>
+        <v>571648</v>
       </c>
       <c r="R28" t="n">
-        <v>6736616</v>
+        <v>6736781</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3390,10 +3390,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130979095</v>
+        <v>130979098</v>
       </c>
       <c r="B29" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3425,10 +3425,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571648</v>
+        <v>571475</v>
       </c>
       <c r="R29" t="n">
-        <v>6736781</v>
+        <v>6736616</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3709,7 +3709,7 @@
         <v>130983618</v>
       </c>
       <c r="B32" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
         <v>130979099</v>
       </c>
       <c r="B34" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>130983069</v>
       </c>
       <c r="B35" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>130983068</v>
       </c>
       <c r="B36" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4345,10 +4345,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130983070</v>
+        <v>130983600</v>
       </c>
       <c r="B38" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4356,34 +4356,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Flytjärnsmyran, Dlr</t>
+          <t>Flytjärnsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>570811</v>
+        <v>571022</v>
       </c>
       <c r="R38" t="n">
-        <v>6736543</v>
+        <v>6736648</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4415,7 +4423,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4425,28 +4433,27 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF38" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4456,7 +4463,7 @@
         <v>130983617</v>
       </c>
       <c r="B39" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4560,10 +4567,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130983600</v>
+        <v>130983070</v>
       </c>
       <c r="B40" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4571,42 +4578,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Flytjärnsmyren, Dlr</t>
+          <t>Flytjärnsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>571022</v>
+        <v>570811</v>
       </c>
       <c r="R40" t="n">
-        <v>6736648</v>
+        <v>6736543</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4638,7 +4637,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4648,27 +4647,28 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4795,7 +4795,7 @@
         <v>130979090</v>
       </c>
       <c r="B42" t="n">
-        <v>79002</v>
+        <v>79003</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>130983065</v>
       </c>
       <c r="B43" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>130983614</v>
       </c>
       <c r="B44" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>130983615</v>
       </c>
       <c r="B45" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         <v>130979085</v>
       </c>
       <c r="B46" t="n">
-        <v>91834</v>
+        <v>91835</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         <v>130983067</v>
       </c>
       <c r="B48" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         <v>130983607</v>
       </c>
       <c r="B51" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5862,10 +5862,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130983616</v>
+        <v>130983612</v>
       </c>
       <c r="B52" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5897,10 +5897,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>570925</v>
+        <v>571254</v>
       </c>
       <c r="R52" t="n">
-        <v>6736674</v>
+        <v>6736555</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5932,7 +5932,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -5942,7 +5942,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5969,10 +5969,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130983612</v>
+        <v>130983616</v>
       </c>
       <c r="B53" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6004,10 +6004,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>571254</v>
+        <v>570925</v>
       </c>
       <c r="R53" t="n">
-        <v>6736555</v>
+        <v>6736674</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6039,7 +6039,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6049,7 +6049,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6076,45 +6076,54 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130983611</v>
+        <v>130983062</v>
       </c>
       <c r="B54" t="n">
-        <v>79245</v>
+        <v>8451</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Flytjärnsmyren, Dlr</t>
+          <t>Flytjärnsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>571283</v>
+        <v>571286</v>
       </c>
       <c r="R54" t="n">
-        <v>6736557</v>
+        <v>6736563</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6146,7 +6155,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6156,7 +6165,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6165,72 +6174,64 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130983062</v>
+        <v>130983611</v>
       </c>
       <c r="B55" t="n">
-        <v>8451</v>
+        <v>79246</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Flytjärnsmyran, Dlr</t>
+          <t>Flytjärnsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>571286</v>
+        <v>571283</v>
       </c>
       <c r="R55" t="n">
-        <v>6736563</v>
+        <v>6736557</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6262,7 +6263,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6272,7 +6273,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6281,19 +6282,18 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6303,7 +6303,7 @@
         <v>130979086</v>
       </c>
       <c r="B56" t="n">
-        <v>91834</v>
+        <v>91835</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6397,10 +6397,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130979094</v>
+        <v>130979100</v>
       </c>
       <c r="B57" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6432,10 +6432,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>571278</v>
+        <v>571473</v>
       </c>
       <c r="R57" t="n">
-        <v>6736783</v>
+        <v>6736490</v>
       </c>
       <c r="S57" t="n">
         <v>1</v>
@@ -6497,7 +6497,7 @@
         <v>130979104</v>
       </c>
       <c r="B58" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6592,10 +6592,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130979100</v>
+        <v>130979094</v>
       </c>
       <c r="B59" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6627,10 +6627,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>571473</v>
+        <v>571278</v>
       </c>
       <c r="R59" t="n">
-        <v>6736490</v>
+        <v>6736783</v>
       </c>
       <c r="S59" t="n">
         <v>1</v>

--- a/artfynd/A 2044-2026 artfynd.xlsx
+++ b/artfynd/A 2044-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY59"/>
+  <dimension ref="A1:AY69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7092862</v>
+        <v>130979085</v>
       </c>
       <c r="B2" t="n">
-        <v>77507</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,39 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>230405</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Flytjärnsmyren, 800 m N om Ändlöstjärnen, Dlr</t>
+          <t>Flytjärnsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571646.1451550075</v>
+        <v>571631</v>
       </c>
       <c r="R2" t="n">
-        <v>6736791.172276019</v>
+        <v>6736722</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,22 +743,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2013-12-03</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2013-12-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>3 fruktkroppar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,33 +762,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Pär Karlsson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Pär Karlsson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7092864</v>
+        <v>130979086</v>
       </c>
       <c r="B3" t="n">
-        <v>77507</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,39 +792,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>230405</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Flytjärnsmyren, 675 m N om Ändlöstjärnen, Dlr</t>
+          <t>Flytjärnsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571547.0273451527</v>
+        <v>571361</v>
       </c>
       <c r="R3" t="n">
-        <v>6736679.192747544</v>
+        <v>6736509</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,22 +846,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2013-12-03</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2013-12-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,44 +866,39 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Pär Karlsson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Pär Karlsson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7092865</v>
+        <v>130872703</v>
       </c>
       <c r="B4" t="n">
-        <v>77507</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -937,21 +907,19 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Flytjärnsmyren, 660 m NNV om Ändlöstjärnen, Dlr</t>
+          <t>Flytjärnsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571143.7600482201</v>
+        <v>570715</v>
       </c>
       <c r="R4" t="n">
-        <v>6736643.77329721</v>
+        <v>6736479</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -975,22 +943,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2013-12-03</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2013-12-03</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,44 +963,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Pär Karlsson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Pär Karlsson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130872700</v>
+        <v>130872707</v>
       </c>
       <c r="B5" t="n">
-        <v>79001</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1052,10 +1010,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571145</v>
+        <v>570828</v>
       </c>
       <c r="R5" t="n">
-        <v>6736812</v>
+        <v>6736602</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1114,14 +1072,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130872713</v>
+        <v>130872708</v>
       </c>
       <c r="B6" t="n">
-        <v>79244</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1149,10 +1107,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570831</v>
+        <v>570829</v>
       </c>
       <c r="R6" t="n">
-        <v>6736787</v>
+        <v>6736515</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1211,32 +1169,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130872697</v>
+        <v>130872709</v>
       </c>
       <c r="B7" t="n">
-        <v>8451</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1246,10 +1204,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570626</v>
+        <v>570714</v>
       </c>
       <c r="R7" t="n">
-        <v>6736614</v>
+        <v>6736567</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1308,32 +1266,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130872699</v>
+        <v>130872710</v>
       </c>
       <c r="B8" t="n">
-        <v>79001</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1343,10 +1301,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571131</v>
+        <v>570585</v>
       </c>
       <c r="R8" t="n">
-        <v>6736687</v>
+        <v>6736756</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1405,14 +1363,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130872707</v>
+        <v>130872711</v>
       </c>
       <c r="B9" t="n">
-        <v>79244</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1440,10 +1398,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>570828</v>
+        <v>570602</v>
       </c>
       <c r="R9" t="n">
-        <v>6736602</v>
+        <v>6736798</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1502,14 +1460,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130872710</v>
+        <v>130872713</v>
       </c>
       <c r="B10" t="n">
-        <v>79244</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1537,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>570585</v>
+        <v>570831</v>
       </c>
       <c r="R10" t="n">
-        <v>6736756</v>
+        <v>6736787</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1599,14 +1557,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130872720</v>
+        <v>130872714</v>
       </c>
       <c r="B11" t="n">
-        <v>79244</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1634,10 +1592,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571020</v>
+        <v>570912</v>
       </c>
       <c r="R11" t="n">
-        <v>6736588</v>
+        <v>6736673</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1696,14 +1654,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130872717</v>
+        <v>130872715</v>
       </c>
       <c r="B12" t="n">
-        <v>79244</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1731,10 +1689,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571254</v>
+        <v>571193</v>
       </c>
       <c r="R12" t="n">
-        <v>6736578</v>
+        <v>6736684</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1793,32 +1751,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130872695</v>
+        <v>130872716</v>
       </c>
       <c r="B13" t="n">
-        <v>79002</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1828,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>570816</v>
+        <v>570988</v>
       </c>
       <c r="R13" t="n">
-        <v>6736802</v>
+        <v>6736647</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1890,32 +1848,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130872698</v>
+        <v>130872717</v>
       </c>
       <c r="B14" t="n">
-        <v>79001</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1925,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>570821</v>
+        <v>571254</v>
       </c>
       <c r="R14" t="n">
-        <v>6736787</v>
+        <v>6736578</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1987,14 +1945,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130872715</v>
+        <v>130872718</v>
       </c>
       <c r="B15" t="n">
-        <v>79244</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2022,10 +1980,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>571193</v>
+        <v>571142</v>
       </c>
       <c r="R15" t="n">
-        <v>6736684</v>
+        <v>6736599</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2084,14 +2042,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130872718</v>
+        <v>130872720</v>
       </c>
       <c r="B16" t="n">
-        <v>79244</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2119,10 +2077,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>571142</v>
+        <v>571020</v>
       </c>
       <c r="R16" t="n">
-        <v>6736599</v>
+        <v>6736588</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2181,14 +2139,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130872714</v>
+        <v>130979092</v>
       </c>
       <c r="B17" t="n">
-        <v>79244</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2216,10 +2174,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>570912</v>
+        <v>570584</v>
       </c>
       <c r="R17" t="n">
-        <v>6736673</v>
+        <v>6736874</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2246,12 +2204,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2278,14 +2236,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130872709</v>
+        <v>130979094</v>
       </c>
       <c r="B18" t="n">
-        <v>79244</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2313,10 +2271,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>570714</v>
+        <v>571278</v>
       </c>
       <c r="R18" t="n">
-        <v>6736567</v>
+        <v>6736783</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2343,12 +2301,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2375,14 +2333,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130872711</v>
+        <v>130979095</v>
       </c>
       <c r="B19" t="n">
-        <v>79244</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2410,10 +2368,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>570602</v>
+        <v>571648</v>
       </c>
       <c r="R19" t="n">
-        <v>6736798</v>
+        <v>6736781</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2440,12 +2398,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2472,32 +2430,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130872696</v>
+        <v>130979096</v>
       </c>
       <c r="B20" t="n">
-        <v>79002</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2507,10 +2465,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>571194</v>
+        <v>571617</v>
       </c>
       <c r="R20" t="n">
-        <v>6736752</v>
+        <v>6736718</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2537,12 +2495,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2569,14 +2527,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130872716</v>
+        <v>130979098</v>
       </c>
       <c r="B21" t="n">
-        <v>79244</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2604,10 +2562,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>570988</v>
+        <v>571475</v>
       </c>
       <c r="R21" t="n">
-        <v>6736647</v>
+        <v>6736616</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2634,12 +2592,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2666,32 +2624,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130872725</v>
+        <v>130979099</v>
       </c>
       <c r="B22" t="n">
-        <v>5177</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2701,10 +2659,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>570869</v>
+        <v>571477</v>
       </c>
       <c r="R22" t="n">
-        <v>6736590</v>
+        <v>6736541</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2731,12 +2689,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2763,14 +2721,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130979096</v>
+        <v>130979100</v>
       </c>
       <c r="B23" t="n">
-        <v>79246</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2798,10 +2756,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>571617</v>
+        <v>571473</v>
       </c>
       <c r="R23" t="n">
-        <v>6736718</v>
+        <v>6736490</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2860,14 +2818,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130983610</v>
+        <v>130979101</v>
       </c>
       <c r="B24" t="n">
-        <v>79246</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -2891,17 +2849,17 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Flytjärnsmyren, Dlr</t>
+          <t>Flytjärnsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>571415</v>
+        <v>570791</v>
       </c>
       <c r="R24" t="n">
-        <v>6736599</v>
+        <v>6736495</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2928,19 +2886,9 @@
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-01-31</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>10:37</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2955,44 +2903,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130979083</v>
+        <v>130979104</v>
       </c>
       <c r="B25" t="n">
-        <v>57073</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3002,10 +2950,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>570745</v>
+        <v>571129</v>
       </c>
       <c r="R25" t="n">
-        <v>6736794</v>
+        <v>6736573</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3040,17 +2988,13 @@
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färsk spillning</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3069,54 +3013,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130983063</v>
+        <v>130983066</v>
       </c>
       <c r="B26" t="n">
-        <v>8451</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Flytjärnsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>570956</v>
+        <v>571463</v>
       </c>
       <c r="R26" t="n">
-        <v>6736657</v>
+        <v>6736779</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3148,7 +3083,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3158,7 +3093,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3186,14 +3121,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130983609</v>
+        <v>130983067</v>
       </c>
       <c r="B27" t="n">
-        <v>79246</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3217,14 +3152,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Flytjärnsmyren, Dlr</t>
+          <t>Flytjärnsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>571481</v>
+        <v>571052</v>
       </c>
       <c r="R27" t="n">
-        <v>6736655</v>
+        <v>6736642</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3256,7 +3191,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3266,7 +3201,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3275,32 +3210,33 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130979095</v>
+        <v>130983068</v>
       </c>
       <c r="B28" t="n">
-        <v>79246</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3328,13 +3264,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571648</v>
+        <v>570849</v>
       </c>
       <c r="R28" t="n">
-        <v>6736781</v>
+        <v>6736706</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3361,43 +3297,54 @@
           <t>2026-01-31</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-01-31</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130979098</v>
+        <v>130983069</v>
       </c>
       <c r="B29" t="n">
-        <v>79246</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3425,13 +3372,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571475</v>
+        <v>570828</v>
       </c>
       <c r="R29" t="n">
-        <v>6736616</v>
+        <v>6736598</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3458,83 +3405,85 @@
           <t>2026-01-31</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-01-31</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130983077</v>
+        <v>130983070</v>
       </c>
       <c r="B30" t="n">
-        <v>5177</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Flytjärnsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>571069</v>
+        <v>570811</v>
       </c>
       <c r="R30" t="n">
-        <v>6736680</v>
+        <v>6736543</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3566,7 +3515,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3576,7 +3525,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3604,32 +3553,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130979089</v>
+        <v>130983075</v>
       </c>
       <c r="B31" t="n">
-        <v>57076</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3639,13 +3588,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>570598</v>
+        <v>570352</v>
       </c>
       <c r="R31" t="n">
-        <v>6736697</v>
+        <v>6736675</v>
       </c>
       <c r="S31" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3672,14 +3621,19 @@
           <t>2026-01-31</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Överflygande</t>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3688,32 +3642,33 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130983618</v>
+        <v>130983607</v>
       </c>
       <c r="B32" t="n">
-        <v>79246</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -3741,10 +3696,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>570808</v>
+        <v>571351</v>
       </c>
       <c r="R32" t="n">
-        <v>6736568</v>
+        <v>6736798</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3776,7 +3731,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3786,7 +3741,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3813,54 +3768,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130983060</v>
+        <v>130983608</v>
       </c>
       <c r="B33" t="n">
-        <v>8451</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Flytjärnsmyran, Dlr</t>
+          <t>Flytjärnsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>570988</v>
+        <v>571369</v>
       </c>
       <c r="R33" t="n">
-        <v>6736721</v>
+        <v>6736788</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3892,7 +3838,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -3902,7 +3848,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3911,33 +3857,32 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130979099</v>
+        <v>130983609</v>
       </c>
       <c r="B34" t="n">
-        <v>79246</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -3961,17 +3906,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Flytjärnsmyran, Dlr</t>
+          <t>Flytjärnsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>571477</v>
+        <v>571481</v>
       </c>
       <c r="R34" t="n">
-        <v>6736541</v>
+        <v>6736655</v>
       </c>
       <c r="S34" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3998,9 +3943,19 @@
           <t>2026-01-31</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4015,26 +3970,26 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130983069</v>
+        <v>130983610</v>
       </c>
       <c r="B35" t="n">
-        <v>79246</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4058,14 +4013,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Flytjärnsmyran, Dlr</t>
+          <t>Flytjärnsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>570828</v>
+        <v>571415</v>
       </c>
       <c r="R35" t="n">
-        <v>6736598</v>
+        <v>6736599</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4097,7 +4052,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4107,7 +4062,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4116,33 +4071,32 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130983068</v>
+        <v>130983611</v>
       </c>
       <c r="B36" t="n">
-        <v>79246</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4166,14 +4120,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Flytjärnsmyran, Dlr</t>
+          <t>Flytjärnsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>570849</v>
+        <v>571283</v>
       </c>
       <c r="R36" t="n">
-        <v>6736706</v>
+        <v>6736557</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4205,7 +4159,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4215,7 +4169,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4224,67 +4178,66 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130979080</v>
+        <v>130983612</v>
       </c>
       <c r="B37" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Flytjärnsmyran, Dlr</t>
+          <t>Flytjärnsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>571221</v>
+        <v>571254</v>
       </c>
       <c r="R37" t="n">
-        <v>6736517</v>
+        <v>6736555</v>
       </c>
       <c r="S37" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4311,14 +4264,19 @@
           <t>2026-01-31</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4333,65 +4291,57 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130983600</v>
+        <v>130983613</v>
       </c>
       <c r="B38" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Flytjärnsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>571022</v>
+        <v>571115</v>
       </c>
       <c r="R38" t="n">
-        <v>6736648</v>
+        <v>6736530</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4423,7 +4373,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4433,14 +4383,14 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="b">
         <v>0</v>
@@ -4460,14 +4410,14 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130983617</v>
+        <v>130983614</v>
       </c>
       <c r="B39" t="n">
-        <v>79246</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -4495,10 +4445,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>570789</v>
+        <v>571012</v>
       </c>
       <c r="R39" t="n">
-        <v>6736672</v>
+        <v>6736611</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4530,7 +4480,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4540,7 +4490,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4567,14 +4517,14 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130983070</v>
+        <v>130983615</v>
       </c>
       <c r="B40" t="n">
-        <v>79246</v>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -4598,14 +4548,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Flytjärnsmyran, Dlr</t>
+          <t>Flytjärnsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>570811</v>
+        <v>570985</v>
       </c>
       <c r="R40" t="n">
-        <v>6736543</v>
+        <v>6736641</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4637,7 +4587,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4647,7 +4597,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4656,73 +4606,63 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130983059</v>
+        <v>130983616</v>
       </c>
       <c r="B41" t="n">
-        <v>8451</v>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Flytjärnsmyran, Dlr</t>
+          <t>Flytjärnsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>571002</v>
+        <v>570925</v>
       </c>
       <c r="R41" t="n">
-        <v>6736760</v>
+        <v>6736674</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4754,7 +4694,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4764,7 +4704,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4773,67 +4713,66 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130979090</v>
+        <v>130983617</v>
       </c>
       <c r="B42" t="n">
-        <v>79003</v>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Flytjärnsmyran, Dlr</t>
+          <t>Flytjärnsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>571620</v>
+        <v>570789</v>
       </c>
       <c r="R42" t="n">
-        <v>6736830</v>
+        <v>6736672</v>
       </c>
       <c r="S42" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4860,9 +4799,19 @@
           <t>2026-01-31</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4877,53 +4826,57 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130983065</v>
+        <v>130983618</v>
       </c>
       <c r="B43" t="n">
-        <v>91834</v>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Flytjärnsmyran, Dlr</t>
+          <t>Flytjärnsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>570827</v>
+        <v>570808</v>
       </c>
       <c r="R43" t="n">
-        <v>6736626</v>
+        <v>6736568</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4955,7 +4908,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -4965,38 +4918,37 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF43" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130983614</v>
+        <v>130872698</v>
       </c>
       <c r="B44" t="n">
-        <v>79246</v>
+        <v>79084</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5004,37 +4956,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Flytjärnsmyren, Dlr</t>
+          <t>Flytjärnsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>571012</v>
+        <v>570821</v>
       </c>
       <c r="R44" t="n">
-        <v>6736611</v>
+        <v>6736787</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5058,22 +5010,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>09:22</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>09:22</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5088,22 +5030,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130983615</v>
+        <v>130872699</v>
       </c>
       <c r="B45" t="n">
-        <v>79246</v>
+        <v>79084</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5111,37 +5053,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Flytjärnsmyren, Dlr</t>
+          <t>Flytjärnsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>570985</v>
+        <v>571131</v>
       </c>
       <c r="R45" t="n">
-        <v>6736641</v>
+        <v>6736687</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5165,22 +5107,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>09:20</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>09:20</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5195,22 +5127,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130979085</v>
+        <v>130872700</v>
       </c>
       <c r="B46" t="n">
-        <v>91835</v>
+        <v>79084</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5218,37 +5150,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Flytjärnsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>571631</v>
+        <v>571145</v>
       </c>
       <c r="R46" t="n">
-        <v>6736722</v>
+        <v>6736812</v>
       </c>
       <c r="S46" t="n">
         <v>1</v>
@@ -5275,17 +5204,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>3 fruktkroppar</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5294,7 +5218,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5313,10 +5236,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130979081</v>
+        <v>130979090</v>
       </c>
       <c r="B47" t="n">
-        <v>57884</v>
+        <v>79084</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5324,21 +5247,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5348,10 +5271,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>571138</v>
+        <v>571620</v>
       </c>
       <c r="R47" t="n">
-        <v>6736573</v>
+        <v>6736830</v>
       </c>
       <c r="S47" t="n">
         <v>1</v>
@@ -5384,11 +5307,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-01-31</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5415,10 +5333,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130983067</v>
+        <v>130979080</v>
       </c>
       <c r="B48" t="n">
-        <v>79246</v>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5426,21 +5344,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5450,13 +5368,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>571052</v>
+        <v>571221</v>
       </c>
       <c r="R48" t="n">
-        <v>6736642</v>
+        <v>6736517</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5483,19 +5401,14 @@
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>09:38</t>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5504,29 +5417,28 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130983056</v>
+        <v>130979081</v>
       </c>
       <c r="B49" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5552,27 +5464,19 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Flytjärnsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>570823</v>
+        <v>571138</v>
       </c>
       <c r="R49" t="n">
-        <v>6736624</v>
+        <v>6736573</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5599,26 +5503,21 @@
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>09:12</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>09:12</t>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="b">
         <v>0</v>
@@ -5626,69 +5525,60 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130983061</v>
+        <v>130979082</v>
       </c>
       <c r="B50" t="n">
-        <v>8451</v>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Flytjärnsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>571287</v>
+        <v>570952</v>
       </c>
       <c r="R50" t="n">
-        <v>6736565</v>
+        <v>6736563</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5715,19 +5605,14 @@
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>10:34</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>10:34</t>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5736,29 +5621,28 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130983607</v>
+        <v>130983055</v>
       </c>
       <c r="B51" t="n">
-        <v>79246</v>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5766,34 +5650,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Flytjärnsmyren, Dlr</t>
+          <t>Flytjärnsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>571351</v>
+        <v>570804</v>
       </c>
       <c r="R51" t="n">
-        <v>6736798</v>
+        <v>6736508</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5825,7 +5717,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5835,7 +5727,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>08:59</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5850,22 +5747,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130983612</v>
+        <v>130983056</v>
       </c>
       <c r="B52" t="n">
-        <v>79246</v>
+        <v>57953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5873,34 +5770,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Flytjärnsmyren, Dlr</t>
+          <t>Flytjärnsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>571254</v>
+        <v>570823</v>
       </c>
       <c r="R52" t="n">
-        <v>6736555</v>
+        <v>6736624</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5932,7 +5837,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -5942,14 +5847,14 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG52" t="b">
         <v>0</v>
@@ -5957,22 +5862,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130983616</v>
+        <v>130983600</v>
       </c>
       <c r="B53" t="n">
-        <v>79246</v>
+        <v>57953</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5980,34 +5885,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Flytjärnsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>570925</v>
+        <v>571022</v>
       </c>
       <c r="R53" t="n">
-        <v>6736674</v>
+        <v>6736648</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6039,7 +5952,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6049,14 +5962,14 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG53" t="b">
         <v>0</v>
@@ -6076,10 +5989,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130983062</v>
+        <v>130979083</v>
       </c>
       <c r="B54" t="n">
-        <v>8451</v>
+        <v>57141</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6087,46 +6000,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Flytjärnsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>571286</v>
+        <v>570745</v>
       </c>
       <c r="R54" t="n">
-        <v>6736563</v>
+        <v>6736794</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6153,19 +6057,14 @@
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>10:34</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>10:34</t>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Färsk spillning</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6174,67 +6073,66 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130983611</v>
+        <v>130872725</v>
       </c>
       <c r="B55" t="n">
-        <v>79246</v>
+        <v>5179</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Flytjärnsmyren, Dlr</t>
+          <t>Flytjärnsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>571283</v>
+        <v>570869</v>
       </c>
       <c r="R55" t="n">
-        <v>6736557</v>
+        <v>6736590</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6258,22 +6156,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>10:33</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>10:33</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6288,60 +6176,69 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130979086</v>
+        <v>130983077</v>
       </c>
       <c r="B56" t="n">
-        <v>91835</v>
+        <v>5179</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5442</v>
+        <v>100526</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Flytjärnsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>571361</v>
+        <v>571069</v>
       </c>
       <c r="R56" t="n">
-        <v>6736509</v>
+        <v>6736680</v>
       </c>
       <c r="S56" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6368,61 +6265,72 @@
           <t>2026-01-31</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2026-01-31</t>
         </is>
       </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130979100</v>
+        <v>130979089</v>
       </c>
       <c r="B57" t="n">
-        <v>79246</v>
+        <v>57144</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6432,10 +6340,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>571473</v>
+        <v>570598</v>
       </c>
       <c r="R57" t="n">
-        <v>6736490</v>
+        <v>6736697</v>
       </c>
       <c r="S57" t="n">
         <v>1</v>
@@ -6468,6 +6376,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Överflygande</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6494,48 +6407,57 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130979104</v>
+        <v>130983054</v>
       </c>
       <c r="B58" t="n">
-        <v>79246</v>
+        <v>5199</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Flytjärnsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>571129</v>
+        <v>571134</v>
       </c>
       <c r="R58" t="n">
-        <v>6736573</v>
+        <v>6736533</v>
       </c>
       <c r="S58" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6562,9 +6484,19 @@
           <t>2026-01-31</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6580,44 +6512,44 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130979094</v>
+        <v>130872697</v>
       </c>
       <c r="B59" t="n">
-        <v>79246</v>
+        <v>8455</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6627,10 +6559,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>571278</v>
+        <v>570626</v>
       </c>
       <c r="R59" t="n">
-        <v>6736783</v>
+        <v>6736614</v>
       </c>
       <c r="S59" t="n">
         <v>1</v>
@@ -6657,12 +6589,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6686,6 +6618,1082 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>130983059</v>
+      </c>
+      <c r="B60" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Flytjärnsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>571002</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6736760</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>130983060</v>
+      </c>
+      <c r="B61" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Flytjärnsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>570988</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6736721</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>130983061</v>
+      </c>
+      <c r="B62" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Flytjärnsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>571287</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6736565</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>130983062</v>
+      </c>
+      <c r="B63" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Flytjärnsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>571286</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6736563</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>130983063</v>
+      </c>
+      <c r="B64" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Flytjärnsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>570956</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6736657</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>130872695</v>
+      </c>
+      <c r="B65" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Flytjärnsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>570816</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6736802</v>
+      </c>
+      <c r="S65" t="n">
+        <v>1</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>130872696</v>
+      </c>
+      <c r="B66" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Flytjärnsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>571194</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6736752</v>
+      </c>
+      <c r="S66" t="n">
+        <v>1</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>7092862</v>
+      </c>
+      <c r="B67" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Flytjärnsmyren, 800 m N om Ändlöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>571646</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6736791</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2013-12-03</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2013-12-03</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Falu Kommun</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Falu Kommun</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>7092864</v>
+      </c>
+      <c r="B68" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Flytjärnsmyren, 675 m N om Ändlöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>571547</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6736679</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2013-12-03</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2013-12-03</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Falu Kommun</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Falu Kommun</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>7092865</v>
+      </c>
+      <c r="B69" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Flytjärnsmyren, 660 m NNV om Ändlöstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>571144</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6736644</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2013-12-03</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2013-12-03</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Falu Kommun</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Falu Kommun</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2044-2026 artfynd.xlsx
+++ b/artfynd/A 2044-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY69"/>
+  <dimension ref="A1:AZ69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983075</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979085</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979086</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130872703</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130872707</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,6 +1304,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130872708</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1371,6 +1406,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130872709</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1468,6 +1508,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130872710</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1565,6 +1610,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130872711</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1662,6 +1712,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130872713</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1759,6 +1814,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130872714</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1856,6 +1916,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130872715</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1953,6 +2018,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130872716</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2050,6 +2120,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130872717</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2147,6 +2222,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130872718</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2244,6 +2324,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130872720</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2341,6 +2426,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979092</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2438,6 +2528,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979094</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2535,6 +2630,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979095</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2632,6 +2732,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979096</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2729,6 +2834,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979098</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2826,6 +2936,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979099</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2923,6 +3038,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979100</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3020,6 +3140,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979101</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3118,6 +3243,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979104</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3226,6 +3356,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983066</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3334,6 +3469,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983067</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3442,6 +3582,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983068</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3550,6 +3695,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983069</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3658,6 +3808,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983070</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3765,6 +3920,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983607</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3872,6 +4032,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983608</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3979,6 +4144,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983609</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4086,6 +4256,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983610</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4193,6 +4368,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983611</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4300,6 +4480,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983612</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4407,6 +4592,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983613</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4514,6 +4704,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983614</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4621,6 +4816,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983615</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4728,6 +4928,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983616</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4835,6 +5040,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983617</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4942,6 +5152,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983618</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5039,6 +5254,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130872698</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5136,6 +5356,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130872699</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5233,6 +5458,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130872700</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5330,6 +5560,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979090</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5432,6 +5667,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979080</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5534,6 +5774,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979081</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5636,6 +5881,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979082</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5756,6 +6006,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983055</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5871,6 +6126,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983056</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5986,6 +6246,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983600</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6088,6 +6353,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979083</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6185,6 +6455,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130872725</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6302,6 +6577,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983077</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6404,6 +6684,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979089</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6521,6 +6806,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983054</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6618,6 +6908,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130872697</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6735,6 +7030,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983059</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6852,6 +7152,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983060</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6969,6 +7274,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983061</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7086,6 +7396,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983062</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7203,6 +7518,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983063</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7300,6 +7620,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130872695</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7397,6 +7722,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130872696</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7496,6 +7826,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7092862</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7595,6 +7930,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7092864</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7694,8 +8034,83 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7092865</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>